--- a/data_extactor/batch_10_fa/batch_0050_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0050_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب خوانده شده | مانیتورینگ | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و پرسنلی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | تشخیص گفتار | وضوح گفتار | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | توجه شنیداری | قدرت تنه | سرعت ادراکی</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | توجه شنیداری | قدرت تنه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | داخل ساختمان، با محیط کنترل‌شده | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان به صورت ایستاده | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض بیماری یا عفونت‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تابش | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تابش | سلامت و ایمنی سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض آلاینده‌ها | ایمیل | آزادی در تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای پیاده‌روی یا دویدن</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای ایستادن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تابش | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | ایمیل | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | دستیاران پزشک | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | پرستاران بیهوشی | تکنسین‌های پزشکی چشم‌پزشکی | پیراپزشکان | جراحان اطفال | فلبوتومیست‌ها | دستیاران پزشک | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی | اورولوژیست‌ها | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | دستیاران پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | پرستاران بیهوشی | تکنسین‌های پزشکی چشم‌پزشکی | پارامدیک‌ها | جراحان کودکان | فلبوتومیست‌ها | دستیاران پزشک | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی | اورولوژیست‌ها | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | نگارش | مانیتورینگ | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | چالاکی انگشتان | ثبات بازو-دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | بینایی دور</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>تماس با دیگران | داخل ساختمان، با محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ایمیل | فراوانی تصمیم‌گیری | قرار گرفتن در معرض بیماری یا عفونت‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فراوانی تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | دستیاران دندانپزشکی | متخصصان پوست | سونوگرافر‌های تشخیصی پزشکی | تکنسین‌های آندوسکوپی | دستیاران پزشک | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | اپتومتریست‌ها | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | دستیاران دندان‌پزشکی | متخصصان پوست | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | دستیاران پزشکی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | FaceTime | Google Drive | سیستم کدگذاری روش‌های معمول مراقبت‌های بهداشتی HCPCS | نرم‌افزار مدیریت تزریق | نرم‌افزار ردیابی موجودی | نرم‌افزار MEDITECH | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | نرم‌افزار مراقبت‌های بهداشتی PointClickCare | نرم‌افزار پردازش نسخه | نرم‌افزار برنامه‌ریزی | نرم‌افزار تریاژ تلفنی | نرم‌افزار مرورگر وب | YouTube | Zoom | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | FaceTime | Google Drive | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار مدیریت تزریق | نرم‌افزار ردیابی موجودی | نرم‌افزار MEDITECH | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | نرم‌افزار مراقبت‌های بهداشتی PointClickCare | نرم‌افزار پردازش نسخه | نرم‌افزار زمان‌بندی | نرم‌افزار تریاژ تلفنی | نرم‌افزار مرورگر وب | YouTube | Zoom | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | درک مطلب خوانده شده | تفکر انتقادی | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | زبان انگلیسی | روانشناسی | پزشکی و دندانپزشکی | اداره و مدیریت | آموزش و تربیت | درمان و مشاوره | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | بیان کتبی | ترتیب‌دهی به اطلاعات | قدرت تنه | قدرت ایستا | انعطاف‌پذیری دسته‌بندی | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | قدرت تنه | قدرت ایستا | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>تماس با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری یا عفونت‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، با محیط کنترل‌شده | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | صرف زمان به صورت ایستاده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان برای پیاده‌روی یا دویدن | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای راه رفتن یا دویدن | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روان‌پزشکی | متخصصان بیهوشی | متخصصان پرستاری بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان طب خانواده | دستیاران سلامت در منزل | دستیاران پزشک | پرستاران بیهوشی | ماماها | پرستاران متخصص | دستیاران پرستاری | دستیاران کاردرمانی | پیراپزشکان | دستیاران فیزیوتراپی | دستیاران پزشک | پرستاران ثبت شده | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | کمک‌یاران سلامت در منزل | دستیاران پزشکی | پرستاران بیهوشی | ماماها | پرستاران متخصص | کمک‌پرستاران | دستیاران کاردرمانی | پارامدیک‌ها | دستیاران فیزیوتراپی | دستیاران پزشک | پرستاران ثبت‌شده | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3M Encoder | Allscripts EHR | Amazing Charts | American Medical Association CodeManager | Azalea Health Azalea EHR | نرم‌افزار صدور صورتحساب | نرم‌افزار پایگاه داده کدگذاری | ComChart EMR | سیستم‌های نمایه‌سازی کامپیوتری | Corel WordPerfect Office Suite | Cyber Records MediChart Express | نرم‌افزار گروه‌بندی DRG | نرم‌افزار تصویربرداری پزشکی DICOM | EHS CareRevolution | Eko | نرم‌افزار پرونده الکترونیک سلامت EMR | سیستم‌های پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | سیستم آرشیو کدگذاری شده EAD | نرم‌افزار کدگذار | EndoSoft | Entity Management Software | Epic Systems | Fox Meadows Accent Data Manager | Fox Meadows ChartingPlus | Fox Meadows EncounterManager | GE Healthcare Logician | نرم‌افزار گرافیکی | Greenway Medical Technologies PrimeChart | HMS | Health Care Data HealthProbe | سیستم کدگذاری روش‌های معمول مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | Holt Systems eMedRec | Hyland Software OnBase | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Lotus 1-2-3 | IBM SPSS Statistics | IDX Systems IDXtend | IDX Systems Patient Chart Tracking | Information Resource Products Clinical Coding Expert | نرم‌افزار Laserfiche | LeonardoMD Renaissance | MD Synergy Medical Appointment Scheduling | نرم‌افزار MEDITECH | MedStar Systems DrWorks | Mediasoft mediOFFICE | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Word | Minitab | NCG Medical Systems d-Chart | NDCMedisoft | NextGen Healthcare Information Systems EMR | PCC EHR | PCC Pediatric Partner | PowerMed | Practice Partner Patient Records | Purkinje Dossier | QMSoftware Receivables Management | Qlik Tech QlikView | Quest Erwin Data Modeler | R | SAP Business Objects | SAP Crystal Reports | SAS | SOAPware EMR | STAT! Systems QD Clinical | ScanSoft Naturally Speaking | نرم‌افزار تصویربرداری Scantron | نرم‌افزار برنامه‌ریزی | Siemens Soarian Financials | Siemens Soarian Scheduling | SoftMed ChartLocater | SoftMed ChartRelease | SoftMed ChartReserve | نرم‌افزار تشخیص گفتار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SynaMed EMR | Tableau | Teradata Database | VantageMed ChartKeeper | نرم‌افزار شبکه خصوصی مجازی VPN | Visionary Medical Systems Visionary OFFICE PM | نرم‌افزار دیکته صوتی | نرم‌افزار مرورگر وب | Welford Chart Notes | e-MDs topsChart | نرم‌افزار eClinicalWorks EHR | eMDs Practice Partner</t>
+          <t>3M Encoder | Allscripts EHR | Amazing Charts | American Medical Association CodeManager | Azalea Health Azalea EHR | نرم‌افزار صدور صورتحساب | نرم‌افزار پایگاه داده کدگذاری | ComChart EMR | سیستم‌های نمایه‌سازی کامپیوتری | Corel WordPerfect Office Suite | Cyber Records MediChart Express | نرم‌افزار گروه‌بندی DRG | نرم‌افزار تصویربرداری پزشکی DICOM | EHS CareRevolution | Eko | نرم‌افزار پرونده الکترونیک سلامت EMR | سیستم‌های پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | سیستم آرشیو کدگذاری شده EAD | نرم‌افزار کدگذار | EndoSoft | Entity Management Software | Epic Systems | Fox Meadows Accent Data Manager | Fox Meadows ChartingPlus | Fox Meadows EncounterManager | GE Healthcare Logician | نرم‌افزار گرافیکی | Greenway Medical Technologies PrimeChart | HMS | Health Care Data HealthProbe | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | Holt Systems eMedRec | Hyland Software OnBase | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Lotus 1-2-3 | IBM SPSS Statistics | IDX Systems IDXtend | IDX Systems Patient Chart Tracking | Information Resource Products Clinical Coding Expert | نرم‌افزار Laserfiche | LeonardoMD Renaissance | MD Synergy Medical Appointment Scheduling | نرم‌افزار MEDITECH | MedStar Systems DrWorks | Mediasoft mediOFFICE | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Word | Minitab | NCG Medical Systems d-Chart | NDCMedisoft | NextGen Healthcare Information Systems EMR | PCC EHR | PCC Pediatric Partner | PowerMed | Practice Partner Patient Records | Purkinje Dossier | QMSoftware Receivables Management | Qlik Tech QlikView | Quest Erwin Data Modeler | R | SAP Business Objects | SAP Crystal Reports | SAS | SOAPware EMR | STAT! Systems QD Clinical | ScanSoft Naturally Speaking | نرم‌افزار تصویربرداری Scantron | نرم‌افزار زمان‌بندی | Siemens Soarian Financials | Siemens Soarian Scheduling | SoftMed ChartLocater | SoftMed ChartRelease | SoftMed ChartReserve | نرم‌افزار تشخیص گفتار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SynaMed EMR | Tableau | Teradata Database | VantageMed ChartKeeper | نرم‌افزار شبکه خصوصی مجازی VPN | Visionary Medical Systems Visionary OFFICE PM | نرم‌افزار دیکته صوتی | نرم‌افزار مرورگر وب | Welford Chart Notes | e-MDs topsChart | نرم‌افزار eClinicalWorks EHR | eMDs Practice Partner</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | کامپیوتر و الکترونیک | زبان انگلیسی | خدمات مشتریان و پرسنلی | اداره و مدیریت | قانون و حکومت | زیست‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، با محیط کنترل‌شده | صرف زمان به صورت نشسته | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های قلب و عروق | متخصصان پرستاری بالینی | متخصصان مدیریت اسناد | پزشکان طب اورژانس | پزشکان طب خانواده | بایگانان اسناد | متخصصان انفورماتیک سلامت | تکنولوژیست‌های اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیلگران مدیریت | دستیاران پزشک | منشی‌های پزشکی و دستیاران اداری | نسخه‌نویسان پزشکی | پرستاران متخصص | کارمندان دفتری عمومی | نمایندگان بیمار | تکنسین‌های داروخانه | فلبوتومیست‌ها | دستیاران پزشک | پرستاران ثبت شده | دستیاران آماری</t>
+          <t>تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پرستاری بالینی | متخصصان مدیریت اسناد | پزشکان طب اورژانس | پزشکان خانواده | کارمندان بایگانی | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | دستیاران پزشکی | منشی‌های پزشکی و دستیاران اداری | نسخه‌نویسان پزشکی | پرستاران متخصص | کارمندان دفتری عمومی | نمایندگان بیمار | تکنسین‌های داروسازی | فلبوتومیست‌ها | دستیاران پزشک | پرستاران ثبت‌شده | دستیاران آماری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | نگارش | مانیتورینگ | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | فروش و بازاریابی | ریاضیات | تولید و فرآوری | اداری | زبان انگلیسی | اداره و مدیریت | آموزش و تربیت | روانشناسی | قانون و حکومت | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | تولید و فرآوری | اداری | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | روان‌شناسی | قانون و دولت | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | چالاکی انگشتان | ترتیب‌دهی به اطلاعات | ثبات بازو-دست | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ‌های بصری | دقت کنترل | چالاکی دست | تقسیم توجه | توجه انتخابی | سرعت ادراکی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | مهارت انگشتان | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | دقت کنترل | مهارت دستی | تقسیم توجه | توجه انتخابی | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ایمیل | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | داخل ساختمان، با محیط کنترل‌شده | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان | دستیاران دندانپزشکی | تکنسین‌های آندوسکوپی | متخصصان سمعک | تکنسین‌های تجهیزات پزشکی | دستیاران پزشک | آماده‌کنندگان تجهیزات پزشکی | تکنسین‌های آزمایشگاه چشم‌پزشکی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | اپتومتریست‌ها | متخصصان ارتوپدی فنی و پروتز | داروسازان | دستیاران داروخانه | تکنسین‌های داروخانه | فلبوتومیست‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | متخصصان مراقبت از پوست | تکنولوژیست‌های جراحی</t>
+          <t>شنوایی‌شناسان | دستیاران دندان‌پزشکی | تکنسین‌های آندوسکوپی | متخصصان سمعک | تکنسین‌های تجهیزات پزشکی | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌های آزمایشگاه چشم‌پزشکی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | متخصصان ارتوپدی فنی و پروتز | داروسازان | دستیاران داروخانه | تکنسین‌های داروسازی | فلبوتومیست‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | متخصصان مراقبت از پوست | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alibre Design | American Orthotic and Prosthetic Association CodingPro | Artsco OrthoPro Complete | Autodesk AutoCAD | نرم‌افزار گرافیک کامپیوتری | نرم‌افزار ایمیل | Futura International O.P.S. | نرم‌افزار آنالیز گام برداشتن | Gez Bowman THE O&amp;P HUB | سیستم کدگذاری روش‌های معمول مراقبت‌های بهداشتی HCPCS | Infinity CAD Systems AutoSculpt | Intuit QuickBooks | MedEvolve eCeno | MedePresence | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OPIE Practice Management Suite | Ohio Willow Wood OMEGA Tracer System | نرم‌افزار مدیریت بیمار | Polhemus FastSCAN | Seattle Systems Shapemaker | Vorum Research Corporation CANFIT-PLUS | نرم‌افزار مرورگر وب</t>
+          <t>Alibre Design | American Orthotic and Prosthetic Association CodingPro | Artsco OrthoPro Complete | Autodesk AutoCAD | نرم‌افزار گرافیک کامپیوتری | نرم‌افزار ایمیل | Futura International O.P.S. | نرم‌افزار تحلیل راه رفتن | Gez Bowman THE O&amp;P HUB | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Infinity CAD Systems AutoSculpt | Intuit QuickBooks | MedEvolve eCeno | MedePresence | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OPIE Practice Management Suite | Ohio Willow Wood OMEGA Tracer System | نرم‌افزار مدیریت بیمار | Polhemus FastSCAN | Seattle Systems Shapemaker | Vorum Research Corporation CANFIT-PLUS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | مانیتورینگ | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | طراحی | درمان و مشاوره | زبان انگلیسی | روانشناسی | مکانیک | آموزش و تربیت | تولید و فرآوری | اداره و مدیریت | مهندسی و فناوری | فیزیک | کامپیوتر و الکترونیک | اداری | زیست‌شناسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | طراحی | درمان و مشاوره | زبان انگلیسی | روان‌شناسی | مکانیک | آموزش و پرورش | تولید و فرآوری | مدیریت و اداره | مهندسی و فناوری | فیزیک | رایانه و الکترونیک | اداری | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | تجسم فضایی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | توجه انتخابی | اصالت | دقت کنترل | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | بینایی دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توجه انتخابی | اصالت | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تماس با دیگران | قرار گرفتن در معرض آلاینده‌ها | داخل ساختمان، با محیط کنترل‌شده | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض بیماری یا عفونت‌ها | قرار گرفتن در معرض شرایط خطرناک | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض شرایط خطرناک | سطح رقابت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | شنوایی‌شناسان | متخصصان قلب | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنسین‌های تجهیزات پزشکی | پرستاران بیهوشی | دستیاران کاردرمانی | ارتودنتیست‌ها | جراحان ارتوپد، به جز اطفال | پیراپزشکان | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | متخصصان بیماری‌های پا | متخصصان پروتزهای دندانی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | شنوایی‌شناسان | متخصصان قلب | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنسین‌های تجهیزات پزشکی | پرستاران بیهوشی | کمک‌یاران کاردرمانی | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | پزشکان پا | متخصصان پروتز دندان | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | مانیتورینگ | یادگیری فعال | نگارش | تفکر انتقادی | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | فروش و بازاریابی | درمان و مشاوره | پزشکی و دندانپزشکی | کامپیوتر و الکترونیک | اداری | زبان انگلیسی | اداره و مدیریت | اقتصاد و حسابداری | روانشناسی | مهندسی و فناوری | آموزش و تربیت | پرسنل و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | درمان و مشاوره | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | اداری | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | روان‌شناسی | مهندسی و فناوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | درک کتبی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | بیان کتبی | توجه انتخابی | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | درک کتبی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ایمیل | داخل ساختمان، با محیط کنترل‌شده | فراوانی تصمیم‌گیری | تماس با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سطح رقابت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>تعامل با مشتریان خارجی یا عموم مردم | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سطح رقابت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان | دستیاران دندانپزشکی | تکنسین‌های آندوسکوپی | دستیاران پزشک | تکنولوژیست‌های نورودیاگنوستیک | دستیاران کاردرمانی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به جز اطفال | متخصصان ارتوپدی فنی و پروتز | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | متخصصان پروتزهای دندانی | آسیب‌شناسان گفتار-زبان | دستیاران آسیب‌شناسی گفتار-زبان | اورولوژیست‌ها</t>
+          <t>شنوایی‌شناسان | دستیاران دندان‌پزشکی | تکنسین‌های آندوسکوپی | دستیاران پزشکی | تکنولوژیست‌های نورودیاگنوستیک | کمک‌یاران کاردرمانی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | متخصصان ارتوپدی فنی و پروتز | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | متخصصان پروتز دندان | آسیب‌شناسان گفتار و زبان | دستیاران آسیب‌شناسی گفتار-زبان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب خوانده شده | تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و پرسنلی | زبان انگلیسی | کامپیوتر و الکترونیک | شیمی | روانشناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | شیمی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | چالاکی انگشتان | ثبات بازو-دست | چالاکی دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | تقسیم توجه | دقت کنترل | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری یا عفونت‌ها | نزدیکی فیزیکی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | پیامد خطا | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | داخل ساختمان، با محیط کنترل‌شده | آزادی در تصمیم‌گیری</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | سونوگرافر‌های تشخیصی پزشکی | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنولوژیست‌های پزشکی هسته‌ای | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های جراحی | تکنسین‌های روان‌پزشکی | تکنسین‌های داروخانه | تکنسین‌های رژیم غذایی | تکنسین‌های پزشکی چشم‌پزشکی | تکنسین‌های آندوسکوپی | آماده‌کنندگان تجهیزات پزشکی | فلبوتومیست‌ها | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران ثبت شده | دوزیمتریست‌های پزشکی | شاغلین مراقبت‌های بهداشتی و کارکنان فنی، همه مشاغل دیگر</t>
+          <t>تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنولوژیست‌های پزشکی هسته‌ای | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های جراحی | تکنسین‌های روانپزشکی | تکنسین‌های داروسازی | تکنسین‌های رژیم غذایی | تکنسین‌های پزشکی چشم‌پزشکی | تکنسین‌های آندوسکوپی | آماده‌سازان تجهیزات پزشکی | فلبوتومیست‌ها | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران ثبت‌شده | دوزیمتریست‌های پزشکی | پزشکان و کارکنان فنی حوزه سلامت، سایر موارد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BESA EEGFocus | Cadwell Laboratories Easy | نرم‌افزار پایگاه داده | EEG Portaview | FileMaker Pro | JavaScript | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Natus NeuroWorks | Neurofax SpikeDetector | Neurotronics Polysmith | R | نرم‌افزار برنامه‌ریزی | نرم‌افزار آنالیز خواب | نرم‌افزار مرورگر وب</t>
+          <t>BESA EEGFocus | Cadwell Laboratories Easy | نرم‌افزار پایگاه داده | EEG Portaview | FileMaker Pro | JavaScript | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Natus NeuroWorks | Neurofax SpikeDetector | Neurotronics Polysmith | R | نرم‌افزار زمان‌بندی | نرم‌افزار آنالیز خواب | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب خوانده شده | مانیتورینگ | نگارش | یادگیری فعال | استدلال‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | پزشکی و دندانپزشکی | زیست‌شناسی | روانشناسی | آموزش و تربیت | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | چالاکی انگشتان | دقت کنترل | ثبات بازو-دست | سرعت بستار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | دقت کنترل | ثبات دست و بازو | سرعت بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>داخل ساختمان، با محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ایمیل | تماس با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری یا عفونت‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ایمیل | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | تکنولوژیست‌های سیتوژنتیک | سونوگرافر‌های تشخیصی پزشکی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنولوژیست‌های سیتوژنتیک | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AcuityPro | Autodesk AutoCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار ایمیل | EyeMD EMR Healthcare Systems EyeMD EMR | پیش‌پردازنده ابرمتن PHP | JavaScript | Medflow Complete | MediPro Medisoft Clinical | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | NaviNet Open | نرم‌افزار SAP | نرم‌افزار مرورگر وب | ezChartWriter | iChartPlus</t>
+          <t>AcuityPro | Autodesk AutoCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار ایمیل | EyeMD EMR Healthcare Systems EyeMD EMR | Hypertext preprocessor PHP | JavaScript | Medflow Complete | MediPro Medisoft Clinical | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | NaviNet Open | نرم‌افزار SAP | نرم‌افزار مرورگر وب | ezChartWriter | iChartPlus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب خوانده شده | نگارش | مانیتورینگ | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و تربیت | ریاضیات | اداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | چالاکی انگشتان | توجه انتخابی | انعطاف‌پذیری بستار | ثبات بازو-دست | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | بینایی دور</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری بستار | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>داخل ساختمان، با محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض بیماری یا عفونت‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | متخصصان پوست | سونوگرافر‌های تشخیصی پزشکی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دستیاران پزشک | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | اپتومتریست‌ها | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پوست | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دستیاران پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0050_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0050_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در ادراک الگو | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | توجه شنیداری | قدرت تنه | سرعت ادراک</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | توجه شنیداری | قدرت تنه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | دستیاران پزشک (Medical Assistants) | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | پرستاران بیهوشی | تکنسین‌های مراقبت‌های چشمی | امدادگران و تکنسین‌های اورژانس (Paramedics) | جراحان اطفال | کارشناسان خون‌گیری (فلبوتومیست‌ها) | دستیاران پزشک (Physician Assistants) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل | متخصصان اورولوژی | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کمک‌پزشکان و دستیاران مطب | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | پرستاران بیهوشی | تکنسین‌های مراقبت‌های چشمی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | کارشناسان و تکنسین‌های خون‌گیری | دستیاران پزشک | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل | متخصصان اورولوژی | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | دید دور</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | دستیاران دندانپزشک | متخصصان پوست | کارشناسان سونوگرافی تشخیصی | تکنسین‌های آندوسکوپی | دستیاران پزشک (Medical Assistants) | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پرتوپزشکان و کارشناسان پرتودرمانی | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | کارشناسان مراقبت‌های تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | دستیاران دندان‌پزشک | متخصصان پوست و مو | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | کمک‌پزشکان و دستیاران مطب | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | پزشکی و دندانپزشکی | مدیریت و امور اداری | آموزش و تدریس | درمان و مشاوره‌ | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | بیان کتبی | مرتب‌سازی اطلاعات | قدرت تنه | قدرت ایستا | انعطاف‌پذیری طبقه‌بندی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | اشتراک زمانی | توجه انتخابی | انعطاف‌پذیری در ادراک الگو | حافظه و به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | قدرت تنه | قدرت ایستا | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پرستاران متخصص روان‌پزشکی | متخصصان بیهوشی | پرستاران بالینی تخصصی | پرستاران مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | مراقبان سلامت در منزل | دستیاران پزشک (Medical Assistants) | پرستاران بیهوشی | ماماها | پرستاران متخصص بالینی (Nurse Practitioners) | کمک‌بهیاران | دستیاران کاردرمانی | امدادگران و تکنسین‌های اورژانس (Paramedics) | دستیاران فیزیوتراپی | دستیاران پزشک (Physician Assistants) | پرستاران دارای پروانه (RN) | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | مراقبان سلامت و بهیاران مراقبت در منزل | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | کمک‌پرستاران | کاردان‌های کاردرمانی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کاردان‌های فیزیوتراپی | دستیاران پزشک | پرستاران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | رایانه و الکترونیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | زیست‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | اشتراک زمانی | چابکی انگشتان | چابکی دستی | دید دور | حافظه و به‌خاطرسپاری | روانی ایده‌ها | سرعت ادراک | انعطاف‌پذیری در ادراک الگو | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان قلب و عروق | پرستاران بالینی تخصصی | کارشناسان مدیریت اسناد و مدارک | پزشکان طب اورژانس | پزشکان عمومی و خانواده | بایگان‌ها و کارمندان پرونده‌ها | کارشناسان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت سرطان و داده‌های بالینی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | دستیاران پزشک (Medical Assistants) | منشی‌ها و دستیاران اداری پزشکی | پیاده‌سازان متون پزشکی (ترانسکریپشنیست‌ها) | پرستاران متخصص بالینی (Nurse Practitioners) | متصدیان امور دفتری | نمایندگان امور مراجعان و بیماران | تکنسین‌های داروخانه | کارشناسان خون‌گیری (فلبوتومیست‌ها) | دستیاران پزشک (Physician Assistants) | پرستاران دارای پروانه (RN) | دستیاران آمار</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | کارشناسان مدیریت اسناد و مدارک | پزشکان طب اورژانس | پزشکان عمومی و خانواده | متصدیان بایگانی و اسناد | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | کمک‌پزشکان و دستیاران مطب | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | پیاده‌سازان و تایپیست‌های متون پزشکی | پرستاران بالینی پیشرفته | متصدیان امور دفتری و امور عمومی اداری | کارشناسان امور بیماران و پذیرش | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کارشناسان و تکنسین‌های خون‌گیری | دستیاران پزشک | پرستاران | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | ریاضیات | تولید و فراوری | امور اداری و دفتری | زبان انگلیسی | مدیریت و امور اداری | آموزش و تدریس | روان‌شناسی | حقوق و مقررات دولتی | رایانه و الکترونیک | امور کارکنان و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | تولید و فرآوری | اداری | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | روان‌شناسی | قانون و دولت | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | چابکی انگشتان | مرتب‌سازی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری طبقه‌بندی | تشخیص رنگ‌ها | دقت کنترل حرکتی | چابکی دستی | اشتراک زمانی | توجه انتخابی | سرعت ادراک | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | مهارت انگشتان | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | دقت کنترل | مهارت دستی | تقسیم توجه | توجه انتخابی | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان (ادیولوژیست‌ها) | دستیاران دندانپزشک | تکنسین‌های آندوسکوپی | کارشناسان تجویز و ساخت سمعک | تکنسین‌های ساخت پروتز و تجهیزات پزشکی | دستیاران پزشک (Medical Assistants) | آماده‌سازان و استریل‌کنندگان تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عدسی | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | داروسازان | کمک‌داروسازان (خدمات دارویی) | تکنسین‌های داروخانه | کارشناسان خون‌گیری (فلبوتومیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | کارشناسان مراقبت از پوست | تکنسین‌های اتاق عمل</t>
+          <t>شنوایی‌شناسان | دستیاران دندان‌پزشک | تکنسین‌های اندوسکوپی | کارشناسان تجویز و ساخت سمعک | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | داروسازان | کمک‌متصدیان داروخانه | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کارشناسان و تکنسین‌های خون‌گیری | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان و تکنسین‌های مراقبت از پوست | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | طراحی | درمان و مشاوره‌ | زبان انگلیسی | روان‌شناسی | مکانیک | آموزش و تدریس | تولید و فراوری | مدیریت و امور اداری | مهندسی و فناوری | فیزیک | رایانه و الکترونیک | امور اداری و دفتری | زیست‌شناسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | طراحی | درمان و مشاوره | زبان انگلیسی | روان‌شناسی | مکانیک | آموزش و پرورش | تولید و فرآوری | مدیریت و اداره | مهندسی و فناوری | فیزیک | رایانه و الکترونیک | اداری | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان کتبی | تجسم فضایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | توجه انتخابی | ابتکار و اصالت طرح | دقت کنترل حرکتی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توجه انتخابی | اصالت | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | شنوایی‌شناسان (ادیولوژیست‌ها) | متخصصان قلب و عروق | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنسین‌های ساخت پروتز و تجهیزات پزشکی | پرستاران بیهوشی | بهیاران و کمک‌های کاردرمانی | متخصصان ارتودنسی | جراحان ارتوپدی (بزرگسالان) | امدادگران و تکنسین‌های اورژانس (Paramedics) | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | متخصصان طب پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | شنوایی‌شناسان | متخصصان بیماری‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | پرستاران بیهوشی | کمک‌یاران کاردرمانی | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | درمان و مشاوره‌ | پزشکی و دندانپزشکی | رایانه و الکترونیک | امور اداری و دفتری | زبان انگلیسی | مدیریت و امور اداری | اقتصاد و حسابداری | روان‌شناسی | مهندسی و فناوری | آموزش و تدریس | امور کارکنان و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | درمان و مشاوره | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | اداری | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | روان‌شناسی | مهندسی و فناوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | درک کتبی | دید نزدیک | استدلال قیاسی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری در ادراک الگو | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | بیان کتبی | توجه انتخابی | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | درک کتبی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان (ادیولوژیست‌ها) | دستیاران دندانپزشک | تکنسین‌های آندوسکوپی | دستیاران پزشک (Medical Assistants) | تکنسین‌های الکترونورودیاگنوستیک | بهیاران و کمک‌های کاردرمانی | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی (بزرگسالان) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | بهیاران فیزیوتراپی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | گفتاردرمانگران (پاتولوژیست‌های گفتار و زبان) | دستیاران گفتاردرمانی | متخصصان اورولوژی</t>
+          <t>شنوایی‌شناسان | دستیاران دندان‌پزشک | تکنسین‌های اندوسکوپی | کمک‌پزشکان و دستیاران مطب | تکنسین‌های الکترونورودیاگنوستیک | کمک‌یاران کاردرمانی | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | ارتوپدهای فنی و سازندگان اعضای مصنوعی | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی) | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | شیمی | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | شیمی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | اشتراک زمانی | دقت کنترل حرکتی | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان قلب و عروق | کارشناسان سونوگرافی تشخیصی | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان پزشکی هسته‌ای | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های اتاق عمل | تکنسین‌های بخش اعصاب و روان | تکنسین‌های داروخانه | تکنسین‌های تغذیه و رژیم‌درمانی | تکنسین‌های مراقبت‌های چشمی | تکنسین‌های آندوسکوپی | آماده‌سازان و استریل‌کنندگان تجهیزات پزشکی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران دارای پروانه (RN) | دوزیمتریست‌های پزشکی | سایر شاغلان حرفه‌ای و تکنسین‌های حوزه سلامت</t>
+          <t>کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های اتاق عمل | تکنسین‌های روان‌پزشکی و بهداشت روان | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | تکنسین‌های مراقبت‌های چشمی | تکنسین‌های اندوسکوپی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان و تکنسین‌های خون‌گیری | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران | دزیمتریست‌های پزشکی | سایر کارشناسان و متخصصان حوزه سلامت و بهداشت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | آموزش و تدریس | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در ادراک الگو | انعطاف‌پذیری طبقه‌بندی | چابکی انگشتان | دقت کنترل حرکتی | ثبات دست و بازو | سرعت ادراک الگو</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | دقت کنترل | ثبات دست و بازو | سرعت بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های سیتوژنتیک | کارشناسان سونوگرافی تشخیصی | تکنسین‌های آندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | کارشناسان پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | پرتوپزشکان و کارشناسان پرتودرمانی | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها | کارشناسان مراقبت‌های تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سیتوژنتیک | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و تدریس | ریاضیات | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | چابکی انگشتان | توجه انتخابی | انعطاف‌پذیری در ادراک الگو | ثبات دست و بازو | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | دید دور</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری بستار | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | متخصصان پوست | کارشناسان سونوگرافی تشخیصی | تکنسین‌های آندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دستیاران پزشک (Medical Assistants) | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پرتوپزشکان و کارشناسان پرتودرمانی | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | متخصصان پوست و مو | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کمک‌پزشکان و دستیاران مطب | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
